--- a/Session3/assignment_05.xlsx
+++ b/Session3/assignment_05.xlsx
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="J92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="b">
         <v>1</v>
@@ -9206,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="n">
+      <c r="Q92" t="b">
         <v>1</v>
       </c>
       <c r="R92" t="inlineStr"/>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>התשובה היא סירוב מנומק - הסוכן מציין שלא נמצא מידע על מדיניות ביטול במסמכים שסופקו, ומפרט מה כן קיים בהם (הצטרפות, דמי השתתפות, כיסויים). אין טענות מומצאות שאינן נתמכות בפלט הסוכן - הטענה תואמת במדויק את פלט הסוכן עצמו.</t>
+          <t>הסוכן סירב לספק מידע שלא נמצא במסמכים, ולא בדה טענות עובדתיות. זהו מקרה של סירוב לגיטימי (not_applicable) ולא חוסר נאמנות.</t>
         </is>
       </c>
       <c r="U92" t="n">
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="J94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="b">
         <v>1</v>
@@ -9395,7 +9395,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="n">
+      <c r="Q94" t="b">
         <v>1</v>
       </c>
       <c r="R94" t="inlineStr"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>הסוכן הודיע שלא נמצא מידע רלוונטי במסמכים, וזו תשובת סירוב עניינית ולא טענה שהומצאה. לכן הקריטריון של נאמנות אינו רלוונטי (not_applicable).</t>
+          <t>הסוכן סירב לענות מכיוון שלא מצא מידע רלוונטי במסמכים שסופקו לו, וציין זאת במפורש. אין כאן טענות מומצאות - הסירוב עצמו נתמך בפלט הסוכן, ולכן מתאים לסיווג not_applicable.</t>
         </is>
       </c>
       <c r="U94" t="n">
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="J96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="b">
         <v>1</v>
@@ -9584,7 +9584,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="n">
+      <c r="Q96" t="b">
         <v>1</v>
       </c>
       <c r="R96" t="inlineStr"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>התשובה היא סירוב מנומק (המסמכים אינם מכילים את המידע המבוקש), ולכן אין טענות עובדתיות חדשות שצריך לבדוק מולן - התשובה תואמת ישירות את פלט הסוכן.</t>
+          <t>הסוכן הצהיר שלא נמצא מידע רלוונטי במסמכים, במקום להמציא תשובה. זהו סירוב לגיטימי כאשר המידע אכן חסר, ולכן הנאמנות מסווגת כ-not_applicable.</t>
         </is>
       </c>
       <c r="U96" t="n">
@@ -9773,7 +9773,7 @@
         <v>3</v>
       </c>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="n">
+      <c r="Q98" t="b">
         <v>0</v>
       </c>
       <c r="R98" t="inlineStr"/>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>הסוכן הצהיר במפורש שלא מצא את המידע במסמכים, ולא בדה טענות עובדתיות - זהו סירוב לגיטימי (not_applicable) ולא חוסר נאמנות.</t>
+          <t>הסוכן הודה שלא מצא את המידע במסמכים ולא בדה טענות; זו תשובת סירוב לגיטימית, ולכן היא not_applicable ולא unfaithful.</t>
         </is>
       </c>
       <c r="U98" t="n">
@@ -9962,7 +9962,7 @@
         <v>3</v>
       </c>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="n">
+      <c r="Q100" t="b">
         <v>0</v>
       </c>
       <c r="R100" t="inlineStr"/>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>הסוכן הצהיר במפורש שלא נמצא מידע במסמכים, ולא בדה טענות. זוהי תשובת סירוב לגיטימית, ולכן not_applicable ולא unfaithful.</t>
+          <t>The final answer is a refusal stating the information could not be found, rather than a fabricated claim. Since no factual claim is made beyond acknowledging failure to find the answer, this is a not_applicable case rather than unfaithful.</t>
         </is>
       </c>
       <c r="U100" t="n">
@@ -10151,7 +10151,7 @@
         <v>3</v>
       </c>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="n">
+      <c r="Q102" t="b">
         <v>0</v>
       </c>
       <c r="R102" t="inlineStr"/>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>הסוכן סירב לענות לאחר שלא מצא את המידע במסמכים שסופקו, ולא בדה טענות. סירוב עקב חוסר מידע נחשב not_applicable ולא unfaithful.</t>
+          <t>הסוכן הודה במפורש שלא מצא את המידע הנדרש ולא בדה טענות - זהו סירוב לגיטימי כאשר המידע לא נמצא, ולכן לא רלוונטי לשפוט כאמינות/אי-אמינות.</t>
         </is>
       </c>
       <c r="U102" t="n">
@@ -11451,11 +11451,7 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11548,11 +11544,7 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11645,11 +11637,7 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
           <t>{}</t>
@@ -11743,11 +11731,7 @@
       <c r="P119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
           <t>{"researcher": true}</t>
@@ -11840,11 +11824,7 @@
       <c r="P120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
           <t>{"researcher": true}</t>
@@ -11937,11 +11917,7 @@
       <c r="P121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
           <t>{}</t>
